--- a/기준/2026 AI.xlsx
+++ b/기준/2026 AI.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="L:\Data\014 회사기타업무\06 AI 설계\1. AI 지급현황\2026\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C2ABDA03-E5CC-4C0A-B311-C75E6E030840}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{C456F790-7C99-43F5-9932-945B10CEC4FF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="38280" yWindow="-120" windowWidth="38640" windowHeight="21240" xr2:uid="{E3FEFC5C-A68B-416E-B2BE-4AB0995DC64C}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="104">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="201" uniqueCount="105">
   <si>
     <t>본부별 공용 유료 AI</t>
     <phoneticPr fontId="2" type="noConversion"/>
@@ -363,10 +363,6 @@
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
   <si>
-    <t>이석영 실장</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
     <t>이인심 소장</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
@@ -447,6 +443,14 @@
   </si>
   <si>
     <t>기타</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>이충희 팀장</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>max플랜으로 상향 완료</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1849,9 +1853,11 @@
       <c r="G59" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="H59" s="4"/>
+      <c r="H59" s="4" t="s">
+        <v>51</v>
+      </c>
       <c r="I59" s="4" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="60" spans="1:9" x14ac:dyDescent="0.3">
@@ -1862,10 +1868,10 @@
         <v>81</v>
       </c>
       <c r="C60" s="2" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="D60" s="7" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
       <c r="E60" s="3">
         <v>100</v>
@@ -1874,8 +1880,12 @@
         <v>7</v>
       </c>
       <c r="G60" s="2"/>
-      <c r="H60" s="2"/>
-      <c r="I60" s="2"/>
+      <c r="H60" s="2">
+        <v>8043</v>
+      </c>
+      <c r="I60" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="61" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A61" s="17"/>
@@ -1893,13 +1903,13 @@
         <v>73</v>
       </c>
       <c r="B62" s="2" t="s">
-        <v>82</v>
+        <v>103</v>
       </c>
       <c r="C62" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D62" s="7" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="E62" s="3">
         <v>100</v>
@@ -1908,8 +1918,12 @@
         <v>7</v>
       </c>
       <c r="G62" s="2"/>
-      <c r="H62" s="2"/>
-      <c r="I62" s="2"/>
+      <c r="H62" s="2">
+        <v>1537</v>
+      </c>
+      <c r="I62" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="63" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A63" s="17"/>
@@ -1927,13 +1941,13 @@
         <v>74</v>
       </c>
       <c r="B64" s="2" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="C64" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D64" s="7" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="E64" s="3">
         <v>100</v>
@@ -1942,8 +1956,12 @@
         <v>7</v>
       </c>
       <c r="G64" s="2"/>
-      <c r="H64" s="2"/>
-      <c r="I64" s="2"/>
+      <c r="H64" s="2">
+        <v>1537</v>
+      </c>
+      <c r="I64" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="65" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A65" s="17"/>
@@ -1961,13 +1979,13 @@
         <v>75</v>
       </c>
       <c r="B66" s="2" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="C66" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D66" s="7" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="E66" s="3">
         <v>100</v>
@@ -1976,27 +1994,37 @@
         <v>7</v>
       </c>
       <c r="G66" s="2"/>
-      <c r="H66" s="2"/>
-      <c r="I66" s="2"/>
+      <c r="H66" s="2">
+        <v>1537</v>
+      </c>
+      <c r="I66" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="67" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A67" s="17"/>
       <c r="B67" s="2" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C67" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D67" s="7" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="E67" s="3">
         <v>100</v>
       </c>
-      <c r="F67" s="2"/>
+      <c r="F67" s="2">
+        <v>8</v>
+      </c>
       <c r="G67" s="2"/>
-      <c r="H67" s="2"/>
-      <c r="I67" s="2"/>
+      <c r="H67" s="2">
+        <v>1537</v>
+      </c>
+      <c r="I67" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="68" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A68" s="17"/>
@@ -2014,21 +2042,27 @@
         <v>76</v>
       </c>
       <c r="B69" s="2" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="C69" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D69" s="7" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="E69" s="3">
         <v>100</v>
       </c>
-      <c r="F69" s="2"/>
+      <c r="F69" s="2">
+        <v>8</v>
+      </c>
       <c r="G69" s="2"/>
-      <c r="H69" s="2"/>
-      <c r="I69" s="2"/>
+      <c r="H69" s="2">
+        <v>1537</v>
+      </c>
+      <c r="I69" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="70" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A70" s="17"/>
@@ -2046,21 +2080,27 @@
         <v>77</v>
       </c>
       <c r="B71" s="2" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="C71" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D71" s="7" t="s">
-        <v>98</v>
+        <v>97</v>
       </c>
       <c r="E71" s="3">
         <v>100</v>
       </c>
-      <c r="F71" s="2"/>
+      <c r="F71" s="2">
+        <v>8</v>
+      </c>
       <c r="G71" s="2"/>
-      <c r="H71" s="2"/>
-      <c r="I71" s="2"/>
+      <c r="H71" s="2">
+        <v>1537</v>
+      </c>
+      <c r="I71" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="72" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A72" s="17"/>
@@ -2078,21 +2118,27 @@
         <v>78</v>
       </c>
       <c r="B73" s="2" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="C73" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D73" s="7" t="s">
-        <v>99</v>
+        <v>98</v>
       </c>
       <c r="E73" s="3">
         <v>100</v>
       </c>
-      <c r="F73" s="2"/>
+      <c r="F73" s="2">
+        <v>8</v>
+      </c>
       <c r="G73" s="2"/>
-      <c r="H73" s="2"/>
-      <c r="I73" s="2"/>
+      <c r="H73" s="2">
+        <v>1537</v>
+      </c>
+      <c r="I73" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="74" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A74" s="17"/>
@@ -2110,21 +2156,27 @@
         <v>79</v>
       </c>
       <c r="B75" s="2" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
       <c r="C75" s="2" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="D75" s="7" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
       <c r="E75" s="3">
         <v>100</v>
       </c>
-      <c r="F75" s="2"/>
+      <c r="F75" s="2">
+        <v>8</v>
+      </c>
       <c r="G75" s="2"/>
-      <c r="H75" s="2"/>
-      <c r="I75" s="2"/>
+      <c r="H75" s="2">
+        <v>1537</v>
+      </c>
+      <c r="I75" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="76" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A76" s="17"/>
@@ -2142,21 +2194,27 @@
         <v>80</v>
       </c>
       <c r="B77" s="2" t="s">
+        <v>89</v>
+      </c>
+      <c r="C77" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="C77" s="2" t="s">
-        <v>91</v>
-      </c>
       <c r="D77" s="7" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
       <c r="E77" s="3">
         <v>100</v>
       </c>
-      <c r="F77" s="2"/>
+      <c r="F77" s="2">
+        <v>8</v>
+      </c>
       <c r="G77" s="2"/>
-      <c r="H77" s="2"/>
-      <c r="I77" s="2"/>
+      <c r="H77" s="2">
+        <v>1537</v>
+      </c>
+      <c r="I77" s="2" t="s">
+        <v>104</v>
+      </c>
     </row>
     <row r="78" spans="1:9" x14ac:dyDescent="0.3">
       <c r="A78" s="17"/>
@@ -2171,6 +2229,16 @@
     </row>
   </sheetData>
   <mergeCells count="17">
+    <mergeCell ref="A69:A70"/>
+    <mergeCell ref="A71:A72"/>
+    <mergeCell ref="A73:A74"/>
+    <mergeCell ref="A75:A76"/>
+    <mergeCell ref="A77:A78"/>
+    <mergeCell ref="A3:A4"/>
+    <mergeCell ref="A5:A6"/>
+    <mergeCell ref="A9:A10"/>
+    <mergeCell ref="A60:A61"/>
+    <mergeCell ref="A62:A63"/>
     <mergeCell ref="A64:A65"/>
     <mergeCell ref="A66:A68"/>
     <mergeCell ref="A50:A52"/>
@@ -2178,16 +2246,6 @@
     <mergeCell ref="A32:A33"/>
     <mergeCell ref="A34:A37"/>
     <mergeCell ref="A46:A49"/>
-    <mergeCell ref="A3:A4"/>
-    <mergeCell ref="A5:A6"/>
-    <mergeCell ref="A9:A10"/>
-    <mergeCell ref="A60:A61"/>
-    <mergeCell ref="A62:A63"/>
-    <mergeCell ref="A69:A70"/>
-    <mergeCell ref="A71:A72"/>
-    <mergeCell ref="A73:A74"/>
-    <mergeCell ref="A75:A76"/>
-    <mergeCell ref="A77:A78"/>
   </mergeCells>
   <phoneticPr fontId="2" type="noConversion"/>
   <hyperlinks>
